--- a/database.xlsx
+++ b/database.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15760" firstSheet="5" activeTab="4"/>
+    <workbookView windowHeight="15800" firstSheet="5" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="zodiacs" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="317">
   <si>
     <t>zodiacID</t>
   </si>
@@ -124,40 +124,79 @@
     <t>blessing</t>
   </si>
   <si>
+    <t>blessingEn</t>
+  </si>
+  <si>
     <t>金運</t>
   </si>
   <si>
+    <t>kinun</t>
+  </si>
+  <si>
     <t>商売繁盛</t>
   </si>
   <si>
+    <t>shobai_hanjo</t>
+  </si>
+  <si>
     <t>勝運・仕事運</t>
   </si>
   <si>
+    <t>shoun_shigotoun</t>
+  </si>
+  <si>
     <t>縁結び</t>
   </si>
   <si>
+    <t>enmusubi</t>
+  </si>
+  <si>
     <t>家内安全</t>
   </si>
   <si>
+    <t>kanai_anzen</t>
+  </si>
+  <si>
     <t>子宝</t>
   </si>
   <si>
+    <t>kodakara</t>
+  </si>
+  <si>
     <t>学業成就</t>
   </si>
   <si>
+    <t>gakugyo_joju</t>
+  </si>
+  <si>
     <t>健康</t>
   </si>
   <si>
+    <t>kenko</t>
+  </si>
+  <si>
     <t>厄除け</t>
   </si>
   <si>
+    <t>yakuyoke</t>
+  </si>
+  <si>
     <t>交通安全</t>
   </si>
   <si>
+    <t>kotsu_anzen</t>
+  </si>
+  <si>
     <t>心願成就</t>
   </si>
   <si>
+    <t>shingan_joju</t>
+  </si>
+  <si>
     <t>開運</t>
+  </si>
+  <si>
+    <t>kaiun</t>
   </si>
   <si>
     <t>spotID</t>
@@ -2135,7 +2174,8 @@
   <cols>
     <col min="1" max="1" width="12.5384615384615" style="12" customWidth="1"/>
     <col min="2" max="2" width="16.0288461538462" style="12" customWidth="1"/>
-    <col min="3" max="16384" width="8.73076923076923" style="12"/>
+    <col min="3" max="3" width="19.8461538461538" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="8.73076923076923" style="12"/>
   </cols>
   <sheetData>
     <row r="1" s="12" customFormat="1" spans="1:3">
@@ -2145,16 +2185,20 @@
       <c r="B1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="13"/>
+      <c r="C1" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2" s="12" customFormat="1" spans="1:5">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="13"/>
+        <v>30</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="D2" s="14"/>
       <c r="E2" s="13"/>
     </row>
@@ -2163,9 +2207,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="13"/>
+        <v>32</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="D3" s="14"/>
     </row>
     <row r="4" s="12" customFormat="1" spans="1:4">
@@ -2173,9 +2219,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="13"/>
+        <v>34</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
       <c r="D4" s="14"/>
     </row>
     <row r="5" s="12" customFormat="1" spans="1:4">
@@ -2183,9 +2231,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="13"/>
+        <v>36</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>37</v>
+      </c>
       <c r="D5" s="14"/>
     </row>
     <row r="6" s="12" customFormat="1" spans="1:4">
@@ -2193,9 +2243,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="13"/>
+        <v>38</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="D6" s="14"/>
     </row>
     <row r="7" s="12" customFormat="1" spans="1:4">
@@ -2203,9 +2255,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="13"/>
+        <v>40</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>41</v>
+      </c>
       <c r="D7" s="14"/>
     </row>
     <row r="8" s="12" customFormat="1" spans="1:4">
@@ -2213,9 +2267,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="13"/>
+        <v>42</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="D8" s="14"/>
     </row>
     <row r="9" s="12" customFormat="1" spans="1:4">
@@ -2223,9 +2279,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="13"/>
+        <v>44</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="D9" s="14"/>
     </row>
     <row r="10" s="12" customFormat="1" spans="1:4">
@@ -2233,9 +2291,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="13"/>
+        <v>46</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="D10" s="14"/>
     </row>
     <row r="11" spans="1:4">
@@ -2243,24 +2303,33 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="14"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3">
       <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>50</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="12">
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>40</v>
+        <v>52</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2288,25 +2357,25 @@
   <sheetData>
     <row r="1" ht="17" spans="1:7">
       <c r="A1" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:8">
@@ -2317,22 +2386,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:8">
@@ -2343,22 +2412,22 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:8">
@@ -2369,22 +2438,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:8">
@@ -2395,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:8">
@@ -2421,22 +2490,22 @@
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:8">
@@ -2447,22 +2516,22 @@
         <v>2</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:8">
@@ -2473,22 +2542,22 @@
         <v>2</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:8">
@@ -2499,22 +2568,22 @@
         <v>2</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:8">
@@ -2525,22 +2594,22 @@
         <v>3</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:8">
@@ -2551,22 +2620,22 @@
         <v>3</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:8">
@@ -2577,22 +2646,22 @@
         <v>3</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:8">
@@ -2603,22 +2672,22 @@
         <v>3</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:8">
@@ -2629,22 +2698,22 @@
         <v>4</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:8">
@@ -2655,22 +2724,22 @@
         <v>4</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:8">
@@ -2681,22 +2750,22 @@
         <v>4</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:8">
@@ -2707,22 +2776,22 @@
         <v>4</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:8">
@@ -2733,22 +2802,22 @@
         <v>5</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:8">
@@ -2759,22 +2828,22 @@
         <v>5</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:8">
@@ -2785,22 +2854,22 @@
         <v>5</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:8">
@@ -2811,22 +2880,22 @@
         <v>5</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:8">
@@ -2837,22 +2906,22 @@
         <v>6</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:8">
@@ -2863,22 +2932,22 @@
         <v>6</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" ht="17" spans="1:8">
@@ -2889,22 +2958,22 @@
         <v>6</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:8">
@@ -2915,22 +2984,22 @@
         <v>6</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3131,10 +3200,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4510,16 +4579,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4527,13 +4596,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4541,13 +4610,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4555,13 +4624,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4569,13 +4638,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4583,13 +4652,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4597,13 +4666,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4611,13 +4680,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4625,13 +4694,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4639,13 +4708,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4653,13 +4722,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4667,13 +4736,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4681,13 +4750,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4695,13 +4764,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4709,13 +4778,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4723,13 +4792,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4737,13 +4806,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4751,13 +4820,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4765,13 +4834,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4779,13 +4848,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4793,13 +4862,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4807,13 +4876,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4821,13 +4890,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4835,13 +4904,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4849,13 +4918,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4863,13 +4932,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4877,13 +4946,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4891,13 +4960,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4905,13 +4974,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4919,13 +4988,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -4933,13 +5002,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -4947,13 +5016,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -4961,13 +5030,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -4975,13 +5044,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -4989,13 +5058,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5003,13 +5072,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5017,13 +5086,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -5048,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:2">

--- a/database.xlsx
+++ b/database.xlsx
@@ -4,15 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800" firstSheet="5" activeTab="1"/>
+    <workbookView windowHeight="15800" firstSheet="5" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="zodiacs" sheetId="1" r:id="rId1"/>
     <sheet name="blessings" sheetId="2" r:id="rId2"/>
     <sheet name="spots" sheetId="4" r:id="rId3"/>
-    <sheet name="spot_blessing" sheetId="5" r:id="rId4"/>
-    <sheet name="proverbs" sheetId="6" r:id="rId5"/>
-    <sheet name="zodiac_proverb" sheetId="7" r:id="rId6"/>
+    <sheet name="spotsOG" sheetId="8" r:id="rId4"/>
+    <sheet name="spot_blessing" sheetId="5" r:id="rId5"/>
+    <sheet name="proverbs" sheetId="6" r:id="rId6"/>
+    <sheet name="zodiac_proverb" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">spots!$A$1:$G$47</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="426">
   <si>
     <t>zodiacID</t>
   </si>
@@ -217,6 +218,9 @@
     <t>spotDesc</t>
   </si>
   <si>
+    <t>site</t>
+  </si>
+  <si>
     <t>大豊神社</t>
   </si>
   <si>
@@ -647,6 +651,330 @@
   </si>
   <si>
     <t>https://kanahebi.cdx.jp/</t>
+  </si>
+  <si>
+    <t>上賀茂神社</t>
+  </si>
+  <si>
+    <t>かみがもじんじゃ</t>
+  </si>
+  <si>
+    <t>京都府京都市北区上賀茂本山339</t>
+  </si>
+  <si>
+    <t>https://www.kamigamojinja.jp/</t>
+  </si>
+  <si>
+    <t>千束八幡神社</t>
+  </si>
+  <si>
+    <t>せんぞくはちまんじんじゃ</t>
+  </si>
+  <si>
+    <t>東京都大田区南千束2-23-10</t>
+  </si>
+  <si>
+    <t>http://www.tokyo-jinjacho.or.jp/ota/5395</t>
+  </si>
+  <si>
+    <t>勝馬神社</t>
+  </si>
+  <si>
+    <t>かちうまじんじゃ</t>
+  </si>
+  <si>
+    <t>茨城県稲敷市阿波958</t>
+  </si>
+  <si>
+    <t>http://oosugi-jinja.or.jp/?page_id=49</t>
+  </si>
+  <si>
+    <t>長等神社</t>
+  </si>
+  <si>
+    <t>ながらじんじゃ</t>
+  </si>
+  <si>
+    <t>滋賀県大津市三井寺町4-1</t>
+  </si>
+  <si>
+    <t>http://nagarajinja.net/index.shtml</t>
+  </si>
+  <si>
+    <t>羊神社（安中市）</t>
+  </si>
+  <si>
+    <t>ひつじじんじゃ</t>
+  </si>
+  <si>
+    <t>群馬県安中市中野谷1751</t>
+  </si>
+  <si>
+    <t>https://www.sakisaki.net/pages/45/</t>
+  </si>
+  <si>
+    <t>羊神社（名古屋市）</t>
+  </si>
+  <si>
+    <t>愛知県名古屋市北区辻町5-26</t>
+  </si>
+  <si>
+    <t>https://www.city.nagoya.jp/kita/miryoku/1020066/1020067/1020068/1020077.html</t>
+  </si>
+  <si>
+    <t>日吉大社</t>
+  </si>
+  <si>
+    <t>ひよしたいしゃ</t>
+  </si>
+  <si>
+    <t>滋賀県大津市坂本5-1-1</t>
+  </si>
+  <si>
+    <t>https://hiyoshitaisha.jp/</t>
+  </si>
+  <si>
+    <t>日枝神社</t>
+  </si>
+  <si>
+    <t>ひえじんじゃ</t>
+  </si>
+  <si>
+    <t>東京都千代田区永田町2-10-5</t>
+  </si>
+  <si>
+    <t>https://www.hiejinja.net/</t>
+  </si>
+  <si>
+    <t>猿丸神社</t>
+  </si>
+  <si>
+    <t>さるまるじんじゃ</t>
+  </si>
+  <si>
+    <t>京都府綴喜郡宇治田原町禅定寺粽谷44</t>
+  </si>
+  <si>
+    <t>https://www.sarumarujinja.jp/</t>
+  </si>
+  <si>
+    <t>本折日吉神社</t>
+  </si>
+  <si>
+    <t>もとおりひよしじんじゃ</t>
+  </si>
+  <si>
+    <t>石川県小松市本折町1</t>
+  </si>
+  <si>
+    <t>https://sanno-hiyoshi.org/</t>
+  </si>
+  <si>
+    <t>鷲宮神社</t>
+  </si>
+  <si>
+    <t>わしのみやじんじゃ</t>
+  </si>
+  <si>
+    <t>埼玉県久喜市鷲宮1-6-1</t>
+  </si>
+  <si>
+    <t>http://www.washinomiyajinja.or.jp/</t>
+  </si>
+  <si>
+    <t>長田神社</t>
+  </si>
+  <si>
+    <t>ながたじんじゃ</t>
+  </si>
+  <si>
+    <t>兵庫県神戸市長田区長田町3-1-1</t>
+  </si>
+  <si>
+    <t>https://nagatajinja.jp/</t>
+  </si>
+  <si>
+    <t>鶏石神社</t>
+  </si>
+  <si>
+    <t>けいせきじんじゃ</t>
+  </si>
+  <si>
+    <t>福岡県福岡市東区香椎4-16-1</t>
+  </si>
+  <si>
+    <t>https://keisekijinja.com/</t>
+  </si>
+  <si>
+    <t>石上神宮</t>
+  </si>
+  <si>
+    <t>いそのかみじんぐう</t>
+  </si>
+  <si>
+    <t>奈良県天理市布留町384</t>
+  </si>
+  <si>
+    <t>https://www.isonokami.jp/</t>
+  </si>
+  <si>
+    <t>武蔵御嶽神社</t>
+  </si>
+  <si>
+    <t>むさしみたけじんじゃ</t>
+  </si>
+  <si>
+    <t>東京都青梅市御岳山176</t>
+  </si>
+  <si>
+    <t>http://musashimitakejinja.jp/</t>
+  </si>
+  <si>
+    <t>霊犬神社</t>
+  </si>
+  <si>
+    <t>れいけんじんじゃ</t>
+  </si>
+  <si>
+    <t>静岡県磐田市見付1010-2</t>
+  </si>
+  <si>
+    <t>https://www.mitsuke-tenjin.com/reikenjinja_reisai/</t>
+  </si>
+  <si>
+    <t>伊奴神社</t>
+  </si>
+  <si>
+    <t>いぬじんじゃ</t>
+  </si>
+  <si>
+    <t>愛知県名古屋市西区稲生町2-12</t>
+  </si>
+  <si>
+    <t>https://inu-jinjya.or.jp/</t>
+  </si>
+  <si>
+    <t>三峯神社</t>
+  </si>
+  <si>
+    <t>みつみねじんじゃ</t>
+  </si>
+  <si>
+    <t>埼玉県秩父市三峰298-1</t>
+  </si>
+  <si>
+    <t>https://www.mitsuminejinja.or.jp/</t>
+  </si>
+  <si>
+    <t>馬見岡綿向神社</t>
+  </si>
+  <si>
+    <t>うまみおかわたむき</t>
+  </si>
+  <si>
+    <t>滋賀県蒲生郡日野町村井711</t>
+  </si>
+  <si>
+    <t>http://www.ex.biwa.ne.jp/~j-watamuki/</t>
+  </si>
+  <si>
+    <t>護王神社</t>
+  </si>
+  <si>
+    <t>ごおうじんじゃ</t>
+  </si>
+  <si>
+    <t>京都府京都市上京区烏丸通下長者町下ル桜鶴圓町385</t>
+  </si>
+  <si>
+    <t>https://www.gooujinja.or.jp/</t>
+  </si>
+  <si>
+    <t>和氣神社</t>
+  </si>
+  <si>
+    <t>わけじんじゃ</t>
+  </si>
+  <si>
+    <t>岡山県和気郡和気町藤野1385</t>
+  </si>
+  <si>
+    <t>https://wake-jinjya.com/</t>
+  </si>
+  <si>
+    <t>足立山妙見宮</t>
+  </si>
+  <si>
+    <t>あだちやまみょうけんぐう</t>
+  </si>
+  <si>
+    <t>福岡県北九州市小倉北区妙見町17-2</t>
+  </si>
+  <si>
+    <t>https://myouken.or.jp/</t>
+  </si>
+  <si>
+    <t>厄除け、開運</t>
+  </si>
+  <si>
+    <t>勝運・仕事運、開運、家内安全</t>
+  </si>
+  <si>
+    <t>健康祈願、勝運・仕事運</t>
+  </si>
+  <si>
+    <t>商売繁栄、縁結び、子宝、健康祈願、厄除け、開運</t>
+  </si>
+  <si>
+    <t>勝運・仕事運、開運、学業成就</t>
+  </si>
+  <si>
+    <t>厄除け、商売繁栄、金運</t>
+  </si>
+  <si>
+    <t>厄除け、縁結び、家内安全、商売繁盛</t>
+  </si>
+  <si>
+    <t>縁結び、勝運・仕事運、商売繁盛、子宝</t>
+  </si>
+  <si>
+    <t>家内安全、健康祈願、交通安全、厄除け、学業成就</t>
+  </si>
+  <si>
+    <t>開運、厄除け</t>
+  </si>
+  <si>
+    <t>商売繁盛、縁結び、交通安全、家内安全、勝運・仕事運、金運、厄除け、健康祈願</t>
+  </si>
+  <si>
+    <t>商売繁盛、厄除け、健康祈願、学業成就</t>
+  </si>
+  <si>
+    <t>健康祈願、厄除け、心願成就</t>
+  </si>
+  <si>
+    <t>厄除け、家内安全、縁結び、子宝、心願成就</t>
+  </si>
+  <si>
+    <t>厄除け、健康祈願、子宝</t>
+  </si>
+  <si>
+    <t>子宝、家内安全、厄除け</t>
+  </si>
+  <si>
+    <t>厄除け、縁結び</t>
+  </si>
+  <si>
+    <t>勝運・仕事運、開運</t>
+  </si>
+  <si>
+    <t>健康祈願、厄除け、子宝</t>
+  </si>
+  <si>
+    <t>健康祈願、厄除け、開運、子宝</t>
+  </si>
+  <si>
+    <t>健康祈願、家内安全、商売繁盛</t>
   </si>
   <si>
     <t>blessingID</t>
@@ -998,7 +1326,7 @@
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1010,6 +1338,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="阿里巴巴普惠体 2.0"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1492,16 +1826,13 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1510,119 +1841,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1638,19 +1972,34 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2018,145 +2367,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="13">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="13">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="13">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="13">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="13">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="13">
+      <c r="A12" s="18">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="13">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="18" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2167,168 +2516,170 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.73076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.5384615384615" style="12" customWidth="1"/>
-    <col min="2" max="2" width="16.0288461538462" style="12" customWidth="1"/>
-    <col min="3" max="3" width="19.8461538461538" style="12" customWidth="1"/>
-    <col min="4" max="16384" width="8.73076923076923" style="12"/>
+    <col min="1" max="1" width="12.5384615384615" style="17" customWidth="1"/>
+    <col min="2" max="2" width="16.0288461538462" style="17" customWidth="1"/>
+    <col min="3" max="3" width="19.8461538461538" style="17" customWidth="1"/>
+    <col min="4" max="16384" width="8.73076923076923" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+    <row r="1" s="17" customFormat="1" spans="1:3">
+      <c r="A1" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" spans="1:5">
-      <c r="A2" s="13">
+    <row r="2" s="17" customFormat="1" spans="1:5">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" s="12" customFormat="1" spans="1:4">
-      <c r="A3" s="13">
+      <c r="D2" s="19"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" s="17" customFormat="1" spans="1:4">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="14"/>
-    </row>
-    <row r="4" s="12" customFormat="1" spans="1:4">
-      <c r="A4" s="13">
+      <c r="D3" s="19"/>
+    </row>
+    <row r="4" s="17" customFormat="1" spans="1:4">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="14"/>
-    </row>
-    <row r="5" s="12" customFormat="1" spans="1:4">
-      <c r="A5" s="13">
+      <c r="D4" s="19"/>
+    </row>
+    <row r="5" s="17" customFormat="1" spans="1:4">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="14"/>
-    </row>
-    <row r="6" s="12" customFormat="1" spans="1:4">
-      <c r="A6" s="13">
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" s="17" customFormat="1" spans="1:4">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" s="12" customFormat="1" spans="1:4">
-      <c r="A7" s="13">
+      <c r="D6" s="19"/>
+    </row>
+    <row r="7" s="17" customFormat="1" spans="1:4">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="14"/>
-    </row>
-    <row r="8" s="12" customFormat="1" spans="1:4">
-      <c r="A8" s="13">
+      <c r="D7" s="19"/>
+    </row>
+    <row r="8" s="17" customFormat="1" spans="1:4">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9" s="12" customFormat="1" spans="1:4">
-      <c r="A9" s="13">
+      <c r="D8" s="19"/>
+    </row>
+    <row r="9" s="17" customFormat="1" spans="1:4">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>健康祈願</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="14"/>
-    </row>
-    <row r="10" s="12" customFormat="1" spans="1:4">
-      <c r="A10" s="13">
+      <c r="D9" s="19"/>
+    </row>
+    <row r="10" s="17" customFormat="1" spans="1:4">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="14"/>
+      <c r="D10" s="19"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="12">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="14"/>
+      <c r="D11" s="19"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="12">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="12">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="17" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2339,7 +2690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
@@ -2355,828 +2706,1315 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:7">
-      <c r="A1" s="7" t="s">
+    <row r="1" ht="17" spans="1:8">
+      <c r="A1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="12" t="s">
         <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2" ht="17" spans="1:8">
-      <c r="A2" s="8">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="13">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="D2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="F2" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="G2" s="14" t="s">
         <v>65</v>
       </c>
+      <c r="H2" s="13" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="3" ht="17" spans="1:8">
-      <c r="A3" s="8">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="13">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="F3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="G3" s="15" t="s">
         <v>71</v>
       </c>
+      <c r="H3" s="13" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="4" ht="17" spans="1:8">
-      <c r="A4" s="8">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="F4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="14" t="s">
         <v>77</v>
       </c>
+      <c r="H4" s="13" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="5" ht="17" spans="1:8">
-      <c r="A5" s="8">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="D5" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="F5" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="14" t="s">
         <v>83</v>
       </c>
+      <c r="H5" s="13" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="6" ht="17" spans="1:8">
-      <c r="A6" s="8">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="13">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="E6" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="G6" s="14" t="s">
         <v>89</v>
       </c>
+      <c r="H6" s="13" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="7" ht="17" spans="1:8">
-      <c r="A7" s="8">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="13">
         <v>2</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="E7" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="F7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="G7" s="14" t="s">
         <v>95</v>
       </c>
+      <c r="H7" s="13" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="8" ht="17" spans="1:8">
-      <c r="A8" s="8">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="13">
         <v>2</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="F8" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="14" t="s">
         <v>101</v>
       </c>
+      <c r="H8" s="13" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="9" ht="17" spans="1:8">
-      <c r="A9" s="8">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="13">
         <v>2</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="E9" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="F9" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="G9" s="14" t="s">
         <v>107</v>
       </c>
+      <c r="H9" s="13" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="10" ht="17" spans="1:8">
-      <c r="A10" s="8">
+      <c r="A10" s="13">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="13">
         <v>3</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="F10" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="14" t="s">
         <v>113</v>
       </c>
+      <c r="H10" s="13" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="11" ht="17" spans="1:8">
-      <c r="A11" s="8">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="13">
         <v>3</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="F11" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="G11" s="14" t="s">
         <v>119</v>
       </c>
+      <c r="H11" s="13" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" ht="17" spans="1:8">
-      <c r="A12" s="8">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="13">
         <v>3</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="G12" s="14" t="s">
         <v>125</v>
       </c>
+      <c r="H12" s="13" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="13" ht="17" spans="1:8">
-      <c r="A13" s="8">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="13">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="C13" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="F13" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="14" t="s">
         <v>131</v>
       </c>
+      <c r="H13" s="13" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="14" ht="17" spans="1:8">
-      <c r="A14" s="8">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="13">
         <v>4</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="C14" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="D14" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="E14" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="F14" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="14" t="s">
         <v>137</v>
       </c>
+      <c r="H14" s="13" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="15" ht="17" spans="1:8">
-      <c r="A15" s="8">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="13">
         <v>4</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="C15" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="E15" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="F15" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="14" t="s">
         <v>143</v>
       </c>
+      <c r="H15" s="13" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="16" ht="17" spans="1:8">
-      <c r="A16" s="8">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="13">
         <v>4</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="C16" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="E16" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="F16" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="G16" s="14" t="s">
         <v>149</v>
       </c>
+      <c r="H16" s="13" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="17" ht="17" spans="1:8">
-      <c r="A17" s="8">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="13">
         <v>4</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="C17" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="E17" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="F17" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="G17" s="14" t="s">
         <v>155</v>
       </c>
+      <c r="H17" s="13" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="18" ht="17" spans="1:8">
-      <c r="A18" s="8">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="13">
         <v>5</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="E18" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="F18" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="G18" s="14" t="s">
         <v>161</v>
       </c>
+      <c r="H18" s="13" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="19" ht="17" spans="1:8">
-      <c r="A19" s="8">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="13">
         <v>5</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="C19" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="D19" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="E19" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="F19" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="G19" s="14" t="s">
         <v>167</v>
       </c>
+      <c r="H19" s="13" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="20" ht="17" spans="1:8">
-      <c r="A20" s="8">
+      <c r="A20" s="13">
         <v>19</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="13">
         <v>5</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="D20" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="E20" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="F20" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="G20" s="14" t="s">
         <v>173</v>
       </c>
+      <c r="H20" s="13" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="21" ht="17" spans="1:8">
-      <c r="A21" s="8">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="13">
         <v>5</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="E21" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="F21" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="G21" s="14" t="s">
         <v>179</v>
       </c>
+      <c r="H21" s="13" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="22" ht="17" spans="1:8">
-      <c r="A22" s="8">
+      <c r="A22" s="13">
         <v>21</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="13">
         <v>6</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="E22" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="F22" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="G22" s="14" t="s">
         <v>185</v>
       </c>
+      <c r="H22" s="13" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="23" ht="17" spans="1:8">
-      <c r="A23" s="8">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="13">
         <v>6</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="C23" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="E23" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="F23" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="G23" s="14" t="s">
         <v>191</v>
       </c>
+      <c r="H23" s="13" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="24" ht="17" spans="1:8">
-      <c r="A24" s="8">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="13">
         <v>6</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="C24" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="D24" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="F24" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="G24" s="14" t="s">
         <v>197</v>
       </c>
+      <c r="H24" s="13" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="25" ht="17" spans="1:8">
-      <c r="A25" s="8">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="13">
         <v>6</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="E25" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="F25" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="G25" s="14" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="11"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="11"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="11"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="11"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="11"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="11"/>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
+      <c r="H25" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" ht="17" spans="1:8">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9">
+        <v>7</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>世界遺産の古社</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>賀茂別雷大神を祀る山城国一宮で、平安京以前から続く古社として世界遺産にも登録される。</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" ht="17" spans="1:8">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9">
+        <v>7</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>池月伝承が残る社</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>洗足池畔に鎮座し、源頼朝の名馬・池月の伝承で知られる八幡神を祀る鎮守。</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" ht="17" spans="1:8">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9">
+        <v>7</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>勝運を祈る馬の社</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>大杉神社境内の末社で、勝馬の名のとおり勝運や仕事運を願う参拝者が訪れる馬ゆかりの社。</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" ht="17" spans="1:8">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9">
+        <v>7</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>三井寺鎮守の古社</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>大津の守り神として古くから信仰され、三井寺周辺を見守る長等山麓の歴史ある神社。</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" ht="34" spans="1:8">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9">
+        <v>8</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>羊守り神を祀る社</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>群馬県安中市中野谷に鎮座し、干支の未にちなみ勝運・開運・学業成就を願う参拝者が訪れる。</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" ht="34" spans="1:8">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9">
+        <v>8</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>名古屋の未年ゆかり社</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>奈良時代創建と伝わり、名古屋で未年の守護として親しまれる全国的にも珍しい羊の神社。</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" ht="17" spans="1:8">
+      <c r="A32" s="9">
+        <v>33</v>
+      </c>
+      <c r="B32" s="9">
+        <v>9</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>比叡山麓の総本宮</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>約2100年の歴史を持つ全国の日吉・日枝・山王神社の総本宮で、比叡山の麓に広大な社殿群を構える。</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" ht="17" spans="1:8">
+      <c r="A33" s="9">
+        <v>34</v>
+      </c>
+      <c r="B33" s="9">
+        <v>9</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>都心を守る山王さま</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>江戸城の鎮守として崇敬された都心の古社で、山王祭でも知られ仕事運や縁結びの祈願を集める。</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" ht="34" spans="1:8">
+      <c r="A34" s="9">
+        <v>35</v>
+      </c>
+      <c r="B34" s="9">
+        <v>9</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>癌封じ祈願の古社</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>百人一首で知られる猿丸大夫を祀り、古くから癌封じ・こぶとりの祈願で信仰を集める宇治田原の社。</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="35" ht="17" spans="1:8">
+      <c r="A35" s="9">
+        <v>36</v>
+      </c>
+      <c r="B35" s="9">
+        <v>9</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>小松鎮護の日吉社</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>富樫家ゆかりの社として創建され、小松の総鎮守として厄除けと開運を祈る人々に親しまれる。</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" ht="17" spans="1:8">
+      <c r="A36" s="9">
+        <v>37</v>
+      </c>
+      <c r="B36" s="9">
+        <v>10</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>関東最古級の大社</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>関東最古級の神社と伝わり、武運長久の信仰とともに地域の総鎮守として長く崇敬されてきた。</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" ht="17" spans="1:8">
+      <c r="A37" s="9">
+        <v>38</v>
+      </c>
+      <c r="B37" s="9">
+        <v>10</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>神功皇后創建の社</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>神功皇后創建と伝わる神戸屈指の古社で、開運招福や厄除けを願う参拝者が絶えない。</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="38" ht="17" spans="1:8">
+      <c r="A38" s="9">
+        <v>39</v>
+      </c>
+      <c r="B38" s="9">
+        <v>10</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>香椎宮境内の鶏石社</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>香椎宮境内に鎮座し、鶏石信仰に基づく心願成就の祈願所として地元で大切に守られている。</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="39" ht="17" spans="1:8">
+      <c r="A39" s="9">
+        <v>40</v>
+      </c>
+      <c r="B39" s="9">
+        <v>10</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>神剣を祀る古宮</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>日本最古級の神宮の一つで、神剣・布都御魂剣を祀る物部氏ゆかりの武門信仰の聖地。</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="40" ht="17" spans="1:8">
+      <c r="A40" s="9">
+        <v>41</v>
+      </c>
+      <c r="B40" s="9">
+        <v>11</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>御岳山頂の霊験社</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>創建二千年以上と伝わる御岳山頂の古社で、おいぬ様信仰と厄除け祈願で関東一円から参拝を集める。</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" ht="17" spans="1:8">
+      <c r="A41" s="9">
+        <v>42</v>
+      </c>
+      <c r="B41" s="9">
+        <v>11</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>しっぺい太郎の霊社</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>見付天神境内にある霊犬悉平太郎を祀る社で、災難除けや健康祈願の守り神として親しまれる。</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="42" ht="17" spans="1:8">
+      <c r="A42" s="9">
+        <v>43</v>
+      </c>
+      <c r="B42" s="9">
+        <v>11</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>安産祈願で名高い社</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>名古屋西部の古社で、犬にちなむ安産・子授けの神徳により家内安全や厄除けの祈願を集める。</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" ht="17" spans="1:8">
+      <c r="A43" s="9">
+        <v>44</v>
+      </c>
+      <c r="B43" s="9">
+        <v>11</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>狼信仰の霊峰神社</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>秩父三峰山に鎮座し、神使の狼信仰と強い厄除けで知られる関東屈指の山岳信仰の社。</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="44" ht="17" spans="1:8">
+      <c r="A44" s="9">
+        <v>45</v>
+      </c>
+      <c r="B44" s="9">
+        <v>12</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>近江日野の総鎮守</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>千年超の歴史を持つ近江日野の総鎮守で、馬と綿向山の名を受け継ぎ地域の開運祈願を支える。</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="45" ht="34" spans="1:8">
+      <c r="A45" s="9">
+        <v>46</v>
+      </c>
+      <c r="B45" s="9">
+        <v>12</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>足腰守護と狛いのしし</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>和気清麻呂公を祀り、狛いのししで知られる京都の社として足腰健康と厄除け祈願で名高い。</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="46" ht="17" spans="1:8">
+      <c r="A46" s="9">
+        <v>47</v>
+      </c>
+      <c r="B46" s="9">
+        <v>12</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>和気清麻呂公ゆかり社</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>和気清麻呂公の出生地近くに鎮座し、猪ゆかりの伝承とともに健康祈願・厄除けで信仰される。</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="47" ht="17" spans="1:8">
+      <c r="A47" s="9">
+        <v>48</v>
+      </c>
+      <c r="B47" s="9">
+        <v>12</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>北斗信仰の妙見宮</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>足立山中腹に鎮座する北斗妙見信仰の古社で、家内安全や商売繁盛、健康祈願の参拝が続く。</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>291</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G47">
@@ -3190,7 +4028,464 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B170"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="20.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="7.5" style="7" customWidth="1"/>
+    <col min="2" max="2" width="9.61538461538461" style="7" customWidth="1"/>
+    <col min="3" max="4" width="14.0384615384615" style="7" customWidth="1"/>
+    <col min="5" max="5" width="68.2596153846154" style="7" customWidth="1"/>
+    <col min="6" max="6" width="14.0384615384615" style="7" customWidth="1"/>
+    <col min="7" max="7" width="10.3846153846154" style="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" spans="1:7">
+      <c r="A1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" ht="51" spans="1:7">
+      <c r="A2" s="9">
+        <v>25</v>
+      </c>
+      <c r="B2" s="9">
+        <v>7</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" ht="51" spans="1:7">
+      <c r="A3" s="9">
+        <v>26</v>
+      </c>
+      <c r="B3" s="9">
+        <v>7</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" ht="34" spans="1:7">
+      <c r="A4" s="9">
+        <v>27</v>
+      </c>
+      <c r="B4" s="9">
+        <v>7</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" ht="34" spans="1:7">
+      <c r="A5" s="9">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
+        <v>7</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" ht="34" spans="1:7">
+      <c r="A6" s="9">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9">
+        <v>8</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" ht="51" spans="1:7">
+      <c r="A7" s="9">
+        <v>30</v>
+      </c>
+      <c r="B7" s="9">
+        <v>8</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" ht="34" spans="1:7">
+      <c r="A8" s="9">
+        <v>33</v>
+      </c>
+      <c r="B8" s="9">
+        <v>9</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" ht="51" spans="1:7">
+      <c r="A9" s="9">
+        <v>34</v>
+      </c>
+      <c r="B9" s="9">
+        <v>9</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" ht="51" spans="1:7">
+      <c r="A10" s="9">
+        <v>35</v>
+      </c>
+      <c r="B10" s="9">
+        <v>9</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" ht="34" spans="1:7">
+      <c r="A11" s="9">
+        <v>36</v>
+      </c>
+      <c r="B11" s="9">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" ht="34" spans="1:7">
+      <c r="A12" s="9">
+        <v>37</v>
+      </c>
+      <c r="B12" s="9">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" ht="51" spans="1:7">
+      <c r="A13" s="9">
+        <v>38</v>
+      </c>
+      <c r="B13" s="9">
+        <v>10</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" ht="51" spans="1:7">
+      <c r="A14" s="9">
+        <v>39</v>
+      </c>
+      <c r="B14" s="9">
+        <v>10</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" ht="34" spans="1:7">
+      <c r="A15" s="9">
+        <v>40</v>
+      </c>
+      <c r="B15" s="9">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" ht="34" spans="1:7">
+      <c r="A16" s="9">
+        <v>41</v>
+      </c>
+      <c r="B16" s="9">
+        <v>11</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" ht="34" spans="1:7">
+      <c r="A17" s="9">
+        <v>42</v>
+      </c>
+      <c r="B17" s="9">
+        <v>11</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" ht="51" spans="1:7">
+      <c r="A18" s="9">
+        <v>43</v>
+      </c>
+      <c r="B18" s="9">
+        <v>11</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" ht="34" spans="1:7">
+      <c r="A19" s="9">
+        <v>44</v>
+      </c>
+      <c r="B19" s="9">
+        <v>11</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" ht="51" spans="1:7">
+      <c r="A20" s="9">
+        <v>45</v>
+      </c>
+      <c r="B20" s="9">
+        <v>12</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" ht="68" spans="1:7">
+      <c r="A21" s="9">
+        <v>46</v>
+      </c>
+      <c r="B21" s="9">
+        <v>12</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" ht="51" spans="1:7">
+      <c r="A22" s="9">
+        <v>47</v>
+      </c>
+      <c r="B22" s="9">
+        <v>12</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23" ht="51" spans="1:7">
+      <c r="A23" s="9">
+        <v>48</v>
+      </c>
+      <c r="B23" s="9">
+        <v>12</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
+  <dimension ref="A1:B178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="8.36538461538461" style="6" customWidth="1"/>
@@ -3198,1364 +4493,1432 @@
     <col min="3" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>spotID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>blessingID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1">
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1">
+    <row r="22">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>8</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>8</v>
+      </c>
+      <c r="B29">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>9</v>
+      </c>
+      <c r="B30">
         <v>1</v>
       </c>
-      <c r="B4" s="1">
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1">
+    <row r="34">
+      <c r="A34">
+        <v>9</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>9</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>9</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>9</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>10</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>10</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>12</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>12</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>13</v>
+      </c>
+      <c r="B49">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>13</v>
+      </c>
+      <c r="B50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>13</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>14</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>14</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>14</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>14</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>14</v>
+      </c>
+      <c r="B56">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>15</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>15</v>
+      </c>
+      <c r="B58">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1">
+    <row r="59">
+      <c r="A59">
+        <v>15</v>
+      </c>
+      <c r="B59">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>16</v>
+      </c>
+      <c r="B60">
         <v>2</v>
       </c>
-      <c r="B6" s="1">
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>16</v>
+      </c>
+      <c r="B61">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1">
+    <row r="62">
+      <c r="A62">
+        <v>16</v>
+      </c>
+      <c r="B62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>16</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>16</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>17</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>17</v>
+      </c>
+      <c r="B66">
         <v>2</v>
       </c>
-      <c r="B7" s="1">
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>17</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>17</v>
+      </c>
+      <c r="B68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>19</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>19</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>19</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>20</v>
+      </c>
+      <c r="B74">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="6">
+    <row r="75">
+      <c r="A75">
+        <v>20</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>20</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>20</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>20</v>
+      </c>
+      <c r="B78">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>20</v>
+      </c>
+      <c r="B79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>20</v>
+      </c>
+      <c r="B80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>21</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>21</v>
+      </c>
+      <c r="B82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>21</v>
+      </c>
+      <c r="B83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>21</v>
+      </c>
+      <c r="B84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>22</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>22</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>22</v>
+      </c>
+      <c r="B87">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>22</v>
+      </c>
+      <c r="B88">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>22</v>
+      </c>
+      <c r="B89">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>23</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>23</v>
+      </c>
+      <c r="B91">
         <v>2</v>
       </c>
-      <c r="B8" s="6">
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>23</v>
+      </c>
+      <c r="B92">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="6">
+    <row r="93">
+      <c r="A93">
+        <v>24</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>24</v>
+      </c>
+      <c r="B94">
         <v>2</v>
       </c>
-      <c r="B9" s="6">
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>24</v>
+      </c>
+      <c r="B95">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>25</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>25</v>
+      </c>
+      <c r="B97">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>26</v>
+      </c>
+      <c r="B98">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="6">
+    <row r="99">
+      <c r="A99">
+        <v>26</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>26</v>
+      </c>
+      <c r="B100">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>27</v>
+      </c>
+      <c r="B101">
         <v>3</v>
       </c>
-      <c r="B10" s="6">
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>27</v>
+      </c>
+      <c r="B102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>28</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>28</v>
+      </c>
+      <c r="B104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>28</v>
+      </c>
+      <c r="B105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>28</v>
+      </c>
+      <c r="B106">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>28</v>
+      </c>
+      <c r="B107">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>28</v>
+      </c>
+      <c r="B108">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>29</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>29</v>
+      </c>
+      <c r="B110">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>29</v>
+      </c>
+      <c r="B111">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>30</v>
+      </c>
+      <c r="B112">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="6">
+    <row r="113">
+      <c r="A113">
+        <v>30</v>
+      </c>
+      <c r="B113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>30</v>
+      </c>
+      <c r="B114">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>31</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>31</v>
+      </c>
+      <c r="B116">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>31</v>
+      </c>
+      <c r="B117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>31</v>
+      </c>
+      <c r="B118">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>32</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>32</v>
+      </c>
+      <c r="B120">
         <v>3</v>
       </c>
-      <c r="B11" s="6">
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>32</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>32</v>
+      </c>
+      <c r="B122">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>33</v>
+      </c>
+      <c r="B123">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="6">
+    <row r="124">
+      <c r="A124">
+        <v>33</v>
+      </c>
+      <c r="B124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>33</v>
+      </c>
+      <c r="B125">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>33</v>
+      </c>
+      <c r="B126">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>34</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>34</v>
+      </c>
+      <c r="B128">
         <v>3</v>
       </c>
-      <c r="B12" s="6">
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>34</v>
+      </c>
+      <c r="B129">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="6">
+    <row r="130">
+      <c r="A130">
+        <v>34</v>
+      </c>
+      <c r="B130">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>35</v>
+      </c>
+      <c r="B131">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>35</v>
+      </c>
+      <c r="B132">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>35</v>
+      </c>
+      <c r="B133">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>35</v>
+      </c>
+      <c r="B134">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>35</v>
+      </c>
+      <c r="B135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>36</v>
+      </c>
+      <c r="B136">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>36</v>
+      </c>
+      <c r="B137">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>37</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>37</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>37</v>
+      </c>
+      <c r="B140">
         <v>3</v>
       </c>
-      <c r="B13" s="6">
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>37</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>37</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>37</v>
+      </c>
+      <c r="B143">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>37</v>
+      </c>
+      <c r="B144">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>37</v>
+      </c>
+      <c r="B145">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>38</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>38</v>
+      </c>
+      <c r="B147">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>38</v>
+      </c>
+      <c r="B148">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>38</v>
+      </c>
+      <c r="B149">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>39</v>
+      </c>
+      <c r="B150">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>40</v>
+      </c>
+      <c r="B151">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>40</v>
+      </c>
+      <c r="B152">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>40</v>
+      </c>
+      <c r="B153">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>41</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>41</v>
+      </c>
+      <c r="B155">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>41</v>
+      </c>
+      <c r="B156">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>41</v>
+      </c>
+      <c r="B157">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>41</v>
+      </c>
+      <c r="B158">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>42</v>
+      </c>
+      <c r="B159">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>42</v>
+      </c>
+      <c r="B160">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>42</v>
+      </c>
+      <c r="B161">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>43</v>
+      </c>
+      <c r="B162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>43</v>
+      </c>
+      <c r="B163">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>43</v>
+      </c>
+      <c r="B164">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>44</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>44</v>
+      </c>
+      <c r="B166">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>45</v>
+      </c>
+      <c r="B167">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>45</v>
+      </c>
+      <c r="B168">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="6">
-        <v>4</v>
-      </c>
-      <c r="B14" s="6">
+    <row r="169">
+      <c r="A169">
+        <v>46</v>
+      </c>
+      <c r="B169">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>46</v>
+      </c>
+      <c r="B170">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>46</v>
+      </c>
+      <c r="B171">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>47</v>
+      </c>
+      <c r="B172">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>47</v>
+      </c>
+      <c r="B173">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>47</v>
+      </c>
+      <c r="B174">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>47</v>
+      </c>
+      <c r="B175">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="6">
-        <v>4</v>
-      </c>
-      <c r="B15" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="6">
-        <v>4</v>
-      </c>
-      <c r="B16" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="6">
-        <v>4</v>
-      </c>
-      <c r="B17" s="6">
+    <row r="176">
+      <c r="A176">
+        <v>48</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>48</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>48</v>
+      </c>
+      <c r="B178">
         <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="6">
-        <v>4</v>
-      </c>
-      <c r="B18" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="6">
-        <v>4</v>
-      </c>
-      <c r="B19" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="6">
-        <v>4</v>
-      </c>
-      <c r="B20" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="6">
-        <v>5</v>
-      </c>
-      <c r="B21" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="6">
-        <v>5</v>
-      </c>
-      <c r="B22" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="6">
-        <v>6</v>
-      </c>
-      <c r="B23" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="6">
-        <v>6</v>
-      </c>
-      <c r="B24" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="6">
-        <v>6</v>
-      </c>
-      <c r="B25" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="6">
-        <v>7</v>
-      </c>
-      <c r="B26" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="6">
-        <v>8</v>
-      </c>
-      <c r="B27" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="6">
-        <v>8</v>
-      </c>
-      <c r="B28" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="6">
-        <v>8</v>
-      </c>
-      <c r="B29" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="6">
-        <v>9</v>
-      </c>
-      <c r="B30" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="6">
-        <v>9</v>
-      </c>
-      <c r="B31" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="6">
-        <v>9</v>
-      </c>
-      <c r="B32" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="6">
-        <v>9</v>
-      </c>
-      <c r="B33" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="6">
-        <v>9</v>
-      </c>
-      <c r="B34" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="6">
-        <v>9</v>
-      </c>
-      <c r="B35" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="6">
-        <v>9</v>
-      </c>
-      <c r="B36" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="6">
-        <v>9</v>
-      </c>
-      <c r="B37" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="6">
-        <v>10</v>
-      </c>
-      <c r="B38" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="6">
-        <v>10</v>
-      </c>
-      <c r="B39" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="6">
-        <v>10</v>
-      </c>
-      <c r="B40" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="6">
-        <v>10</v>
-      </c>
-      <c r="B41" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="6">
-        <v>10</v>
-      </c>
-      <c r="B42" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="6">
-        <v>10</v>
-      </c>
-      <c r="B43" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="6">
-        <v>11</v>
-      </c>
-      <c r="B44" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="6">
-        <v>11</v>
-      </c>
-      <c r="B45" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="6">
-        <v>11</v>
-      </c>
-      <c r="B46" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="6">
-        <v>12</v>
-      </c>
-      <c r="B47" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="6">
-        <v>12</v>
-      </c>
-      <c r="B48" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="6">
-        <v>13</v>
-      </c>
-      <c r="B49" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="6">
-        <v>13</v>
-      </c>
-      <c r="B50" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="6">
-        <v>13</v>
-      </c>
-      <c r="B51" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="6">
-        <v>14</v>
-      </c>
-      <c r="B52" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="6">
-        <v>14</v>
-      </c>
-      <c r="B53" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="6">
-        <v>14</v>
-      </c>
-      <c r="B54" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="6">
-        <v>14</v>
-      </c>
-      <c r="B55" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="6">
-        <v>14</v>
-      </c>
-      <c r="B56" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="6">
-        <v>15</v>
-      </c>
-      <c r="B57" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="6">
-        <v>15</v>
-      </c>
-      <c r="B58" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="6">
-        <v>15</v>
-      </c>
-      <c r="B59" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="6">
-        <v>16</v>
-      </c>
-      <c r="B60" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="6">
-        <v>16</v>
-      </c>
-      <c r="B61" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="6">
-        <v>16</v>
-      </c>
-      <c r="B62" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="6">
-        <v>16</v>
-      </c>
-      <c r="B63" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="6">
-        <v>16</v>
-      </c>
-      <c r="B64" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="6">
-        <v>17</v>
-      </c>
-      <c r="B65" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="6">
-        <v>17</v>
-      </c>
-      <c r="B66" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="6">
-        <v>17</v>
-      </c>
-      <c r="B67" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="6">
-        <v>17</v>
-      </c>
-      <c r="B68" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="6">
-        <v>18</v>
-      </c>
-      <c r="B69" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="6">
-        <v>18</v>
-      </c>
-      <c r="B70" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="6">
-        <v>19</v>
-      </c>
-      <c r="B71" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="6">
-        <v>19</v>
-      </c>
-      <c r="B72" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="6">
-        <v>19</v>
-      </c>
-      <c r="B73" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="6">
-        <v>20</v>
-      </c>
-      <c r="B74" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="6">
-        <v>20</v>
-      </c>
-      <c r="B75" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="6">
-        <v>20</v>
-      </c>
-      <c r="B76" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="6">
-        <v>20</v>
-      </c>
-      <c r="B77" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="6">
-        <v>20</v>
-      </c>
-      <c r="B78" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="6">
-        <v>20</v>
-      </c>
-      <c r="B79" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="6">
-        <v>20</v>
-      </c>
-      <c r="B80" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="6">
-        <v>21</v>
-      </c>
-      <c r="B81" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="6">
-        <v>21</v>
-      </c>
-      <c r="B82" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="6">
-        <v>21</v>
-      </c>
-      <c r="B83" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="6">
-        <v>21</v>
-      </c>
-      <c r="B84" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="6">
-        <v>22</v>
-      </c>
-      <c r="B85" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="6">
-        <v>22</v>
-      </c>
-      <c r="B86" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="6">
-        <v>22</v>
-      </c>
-      <c r="B87" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="6">
-        <v>22</v>
-      </c>
-      <c r="B88" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="6">
-        <v>22</v>
-      </c>
-      <c r="B89" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="6">
-        <v>23</v>
-      </c>
-      <c r="B90" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" s="6">
-        <v>23</v>
-      </c>
-      <c r="B91" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="6">
-        <v>23</v>
-      </c>
-      <c r="B92" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="6">
-        <v>24</v>
-      </c>
-      <c r="B93" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="6">
-        <v>24</v>
-      </c>
-      <c r="B94" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="6">
-        <v>24</v>
-      </c>
-      <c r="B95" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="6">
-        <v>25</v>
-      </c>
-      <c r="B96" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="6">
-        <v>25</v>
-      </c>
-      <c r="B97" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" s="6">
-        <v>26</v>
-      </c>
-      <c r="B98" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="6">
-        <v>26</v>
-      </c>
-      <c r="B99" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="6">
-        <v>26</v>
-      </c>
-      <c r="B100" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="6">
-        <v>27</v>
-      </c>
-      <c r="B101" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="6">
-        <v>27</v>
-      </c>
-      <c r="B102" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="6">
-        <v>28</v>
-      </c>
-      <c r="B103" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="6">
-        <v>28</v>
-      </c>
-      <c r="B104" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="6">
-        <v>28</v>
-      </c>
-      <c r="B105" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" s="6">
-        <v>28</v>
-      </c>
-      <c r="B106" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" s="6">
-        <v>28</v>
-      </c>
-      <c r="B107" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" s="6">
-        <v>28</v>
-      </c>
-      <c r="B108" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" s="6">
-        <v>29</v>
-      </c>
-      <c r="B109" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" s="6">
-        <v>29</v>
-      </c>
-      <c r="B110" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" s="6">
-        <v>29</v>
-      </c>
-      <c r="B111" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" s="6">
-        <v>30</v>
-      </c>
-      <c r="B112" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="6">
-        <v>30</v>
-      </c>
-      <c r="B113" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="6">
-        <v>30</v>
-      </c>
-      <c r="B114" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="6">
-        <v>31</v>
-      </c>
-      <c r="B115" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="6">
-        <v>31</v>
-      </c>
-      <c r="B116" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="6">
-        <v>31</v>
-      </c>
-      <c r="B117" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" s="6">
-        <v>31</v>
-      </c>
-      <c r="B118" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" s="6">
-        <v>32</v>
-      </c>
-      <c r="B119" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="6">
-        <v>32</v>
-      </c>
-      <c r="B120" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="6">
-        <v>32</v>
-      </c>
-      <c r="B121" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="6">
-        <v>32</v>
-      </c>
-      <c r="B122" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="6">
-        <v>33</v>
-      </c>
-      <c r="B123" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="6">
-        <v>33</v>
-      </c>
-      <c r="B124" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="6">
-        <v>33</v>
-      </c>
-      <c r="B125" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="6">
-        <v>33</v>
-      </c>
-      <c r="B126" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="6">
-        <v>33</v>
-      </c>
-      <c r="B127" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="6">
-        <v>34</v>
-      </c>
-      <c r="B128" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="6">
-        <v>34</v>
-      </c>
-      <c r="B129" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="6">
-        <v>35</v>
-      </c>
-      <c r="B130" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="6">
-        <v>35</v>
-      </c>
-      <c r="B131" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="6">
-        <v>35</v>
-      </c>
-      <c r="B132" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="6">
-        <v>35</v>
-      </c>
-      <c r="B133" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="6">
-        <v>35</v>
-      </c>
-      <c r="B134" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="6">
-        <v>35</v>
-      </c>
-      <c r="B135" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="6">
-        <v>35</v>
-      </c>
-      <c r="B136" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="6">
-        <v>35</v>
-      </c>
-      <c r="B137" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="6">
-        <v>36</v>
-      </c>
-      <c r="B138" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="6">
-        <v>36</v>
-      </c>
-      <c r="B139" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="6">
-        <v>36</v>
-      </c>
-      <c r="B140" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="6">
-        <v>36</v>
-      </c>
-      <c r="B141" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="6">
-        <v>37</v>
-      </c>
-      <c r="B142" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="6">
-        <v>38</v>
-      </c>
-      <c r="B143" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="6">
-        <v>38</v>
-      </c>
-      <c r="B144" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="6">
-        <v>38</v>
-      </c>
-      <c r="B145" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="6">
-        <v>39</v>
-      </c>
-      <c r="B146" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="6">
-        <v>39</v>
-      </c>
-      <c r="B147" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="6">
-        <v>39</v>
-      </c>
-      <c r="B148" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="6">
-        <v>39</v>
-      </c>
-      <c r="B149" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="6">
-        <v>39</v>
-      </c>
-      <c r="B150" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="6">
-        <v>40</v>
-      </c>
-      <c r="B151" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="6">
-        <v>40</v>
-      </c>
-      <c r="B152" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="6">
-        <v>40</v>
-      </c>
-      <c r="B153" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="6">
-        <v>41</v>
-      </c>
-      <c r="B154" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="6">
-        <v>41</v>
-      </c>
-      <c r="B155" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="6">
-        <v>41</v>
-      </c>
-      <c r="B156" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="6">
-        <v>42</v>
-      </c>
-      <c r="B157" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="6">
-        <v>42</v>
-      </c>
-      <c r="B158" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="6">
-        <v>43</v>
-      </c>
-      <c r="B159" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="6">
-        <v>43</v>
-      </c>
-      <c r="B160" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="6">
-        <v>44</v>
-      </c>
-      <c r="B161" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="6">
-        <v>44</v>
-      </c>
-      <c r="B162" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="6">
-        <v>44</v>
-      </c>
-      <c r="B163" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="6">
-        <v>45</v>
-      </c>
-      <c r="B164" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="6">
-        <v>45</v>
-      </c>
-      <c r="B165" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="6">
-        <v>45</v>
-      </c>
-      <c r="B166" s="6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="6">
-        <v>45</v>
-      </c>
-      <c r="B167" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="6">
-        <v>46</v>
-      </c>
-      <c r="B168" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="6">
-        <v>46</v>
-      </c>
-      <c r="B169" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="6">
-        <v>46</v>
-      </c>
-      <c r="B170" s="6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4564,7 +5927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D37"/>
@@ -4579,16 +5942,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
-        <v>205</v>
+        <v>314</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>208</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4596,13 +5959,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>209</v>
+        <v>318</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>210</v>
+        <v>319</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>211</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -4610,13 +5973,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>212</v>
+        <v>321</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>214</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4624,13 +5987,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>216</v>
+        <v>325</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>217</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4638,13 +6001,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>218</v>
+        <v>327</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>219</v>
+        <v>328</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>220</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4652,13 +6015,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>223</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4666,13 +6029,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>224</v>
+        <v>333</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>225</v>
+        <v>334</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>226</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4680,13 +6043,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>227</v>
+        <v>336</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>228</v>
+        <v>337</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>229</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4694,13 +6057,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>230</v>
+        <v>339</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>231</v>
+        <v>340</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>232</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4708,13 +6071,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>234</v>
+        <v>343</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>235</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4722,13 +6085,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>236</v>
+        <v>345</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>237</v>
+        <v>346</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>238</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4736,13 +6099,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>239</v>
+        <v>348</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>240</v>
+        <v>349</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>241</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4750,13 +6113,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>242</v>
+        <v>351</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>243</v>
+        <v>352</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>244</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4764,13 +6127,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>245</v>
+        <v>354</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>246</v>
+        <v>355</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>247</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4778,13 +6141,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>248</v>
+        <v>357</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>249</v>
+        <v>358</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>250</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4792,13 +6155,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>251</v>
+        <v>360</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>252</v>
+        <v>361</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>253</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4806,13 +6169,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>254</v>
+        <v>363</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>255</v>
+        <v>364</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>256</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4820,13 +6183,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>257</v>
+        <v>366</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>258</v>
+        <v>367</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>259</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4834,13 +6197,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>260</v>
+        <v>369</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>261</v>
+        <v>370</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>262</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4848,13 +6211,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>263</v>
+        <v>372</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>264</v>
+        <v>373</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>265</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4862,13 +6225,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>266</v>
+        <v>375</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>267</v>
+        <v>376</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>268</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4876,13 +6239,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>269</v>
+        <v>378</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>270</v>
+        <v>379</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4890,13 +6253,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>272</v>
+        <v>381</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>273</v>
+        <v>382</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>274</v>
+        <v>383</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4904,13 +6267,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>275</v>
+        <v>384</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>277</v>
+        <v>386</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4918,13 +6281,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>278</v>
+        <v>387</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>279</v>
+        <v>388</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>280</v>
+        <v>389</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4932,13 +6295,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>281</v>
+        <v>390</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>282</v>
+        <v>391</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>283</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4946,13 +6309,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>284</v>
+        <v>393</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>286</v>
+        <v>395</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4960,13 +6323,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>287</v>
+        <v>396</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>288</v>
+        <v>397</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>289</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4974,13 +6337,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>290</v>
+        <v>399</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>291</v>
+        <v>400</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>292</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4988,13 +6351,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>293</v>
+        <v>402</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>294</v>
+        <v>403</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>295</v>
+        <v>404</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -5002,13 +6365,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>296</v>
+        <v>405</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>297</v>
+        <v>406</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>298</v>
+        <v>407</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -5016,13 +6379,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>299</v>
+        <v>408</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>300</v>
+        <v>409</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>301</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -5030,13 +6393,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>302</v>
+        <v>411</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>303</v>
+        <v>412</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>304</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -5044,13 +6407,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>305</v>
+        <v>414</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>306</v>
+        <v>415</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>307</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -5058,13 +6421,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>308</v>
+        <v>417</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>309</v>
+        <v>418</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>310</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5072,13 +6435,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>311</v>
+        <v>420</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>313</v>
+        <v>422</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -5086,13 +6449,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>314</v>
+        <v>423</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>316</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -5101,7 +6464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B39"/>
@@ -5117,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>205</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:2">
